--- a/data/H131_20260625_18.xlsx
+++ b/data/H131_20260625_18.xlsx
@@ -351,7 +351,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="23" width="8.71"/>
+    <col customWidth="1" min="1" max="9" width="8.71"/>
+    <col customWidth="1" min="10" max="10" width="16.29"/>
+    <col customWidth="1" min="11" max="23" width="8.71"/>
     <col customWidth="1" min="24" max="24" width="19.14"/>
     <col customWidth="1" min="25" max="26" width="8.71"/>
   </cols>
@@ -681,7 +683,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" s="2">
-        <v>632.0</v>
+        <v>633.0</v>
       </c>
       <c r="K5" s="2">
         <v>1.0</v>
@@ -693,10 +695,10 @@
         <v>0.0</v>
       </c>
       <c r="N5" s="2">
-        <v>632.0</v>
+        <v>633.0</v>
       </c>
       <c r="O5" s="2">
-        <v>333.0</v>
+        <v>334.0</v>
       </c>
       <c r="P5" s="2">
         <v>296.0</v>
@@ -708,7 +710,7 @@
         <v>24.0</v>
       </c>
       <c r="S5" s="2">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="T5" s="2">
         <v>1.0</v>
@@ -720,7 +722,7 @@
         <v>0.0</v>
       </c>
       <c r="W5" s="2">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
       <c r="X5" s="1">
         <v>1.0</v>
@@ -1347,7 +1349,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" s="2">
-        <v>1262.0</v>
+        <v>1263.0</v>
       </c>
       <c r="K14" s="2">
         <v>1.0</v>
@@ -1359,19 +1361,19 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="2">
-        <v>1262.0</v>
+        <v>1263.0</v>
       </c>
       <c r="O14" s="2">
         <v>704.0</v>
       </c>
       <c r="P14" s="2">
-        <v>548.0</v>
+        <v>549.0</v>
       </c>
       <c r="Q14" s="2">
         <v>10.0</v>
       </c>
       <c r="R14" s="2">
-        <v>37.0</v>
+        <v>36.0</v>
       </c>
       <c r="S14" s="2">
         <v>37.0</v>
@@ -1386,7 +1388,7 @@
         <v>0.0</v>
       </c>
       <c r="W14" s="2">
-        <v>80.0</v>
+        <v>79.0</v>
       </c>
       <c r="X14" s="1">
         <v>1.0</v>
@@ -1495,7 +1497,7 @@
         <v>692.0</v>
       </c>
       <c r="J16" s="2">
-        <v>595.0</v>
+        <v>597.0</v>
       </c>
       <c r="K16" s="2">
         <v>1.0</v>
@@ -1507,13 +1509,13 @@
         <v>0.0</v>
       </c>
       <c r="N16" s="2">
-        <v>595.0</v>
+        <v>597.0</v>
       </c>
       <c r="O16" s="2">
-        <v>291.0</v>
+        <v>292.0</v>
       </c>
       <c r="P16" s="2">
-        <v>301.0</v>
+        <v>302.0</v>
       </c>
       <c r="Q16" s="2">
         <v>3.0</v>
@@ -1522,19 +1524,19 @@
         <v>30.0</v>
       </c>
       <c r="S16" s="2">
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
       <c r="T16" s="2">
         <v>12.0</v>
       </c>
       <c r="U16" s="2">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="V16" s="2">
         <v>0.0</v>
       </c>
       <c r="W16" s="2">
-        <v>97.0</v>
+        <v>95.0</v>
       </c>
       <c r="X16" s="1">
         <v>1.0</v>
@@ -1643,7 +1645,7 @@
         <v>1182.0</v>
       </c>
       <c r="J18" s="2">
-        <v>1135.0</v>
+        <v>1137.0</v>
       </c>
       <c r="K18" s="2">
         <v>1.0</v>
@@ -1655,10 +1657,10 @@
         <v>0.0</v>
       </c>
       <c r="N18" s="2">
-        <v>1135.0</v>
+        <v>1137.0</v>
       </c>
       <c r="O18" s="2">
-        <v>605.0</v>
+        <v>607.0</v>
       </c>
       <c r="P18" s="2">
         <v>529.0</v>
@@ -1670,7 +1672,7 @@
         <v>25.0</v>
       </c>
       <c r="S18" s="2">
-        <v>43.0</v>
+        <v>41.0</v>
       </c>
       <c r="T18" s="2">
         <v>7.0</v>
@@ -1682,7 +1684,7 @@
         <v>2.0</v>
       </c>
       <c r="W18" s="2">
-        <v>89.0</v>
+        <v>87.0</v>
       </c>
       <c r="X18" s="1">
         <v>1.0</v>
@@ -1717,7 +1719,7 @@
         <v>940.0</v>
       </c>
       <c r="J19" s="2">
-        <v>867.0</v>
+        <v>869.0</v>
       </c>
       <c r="K19" s="2">
         <v>1.0</v>
@@ -1729,10 +1731,10 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="2">
-        <v>867.0</v>
+        <v>869.0</v>
       </c>
       <c r="O19" s="2">
-        <v>468.0</v>
+        <v>470.0</v>
       </c>
       <c r="P19" s="2">
         <v>397.0</v>
@@ -1741,7 +1743,7 @@
         <v>2.0</v>
       </c>
       <c r="R19" s="2">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="S19" s="2">
         <v>28.0</v>
@@ -1750,13 +1752,13 @@
         <v>11.0</v>
       </c>
       <c r="U19" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="V19" s="2">
         <v>0.0</v>
       </c>
       <c r="W19" s="2">
-        <v>73.0</v>
+        <v>71.0</v>
       </c>
       <c r="X19" s="1">
         <v>1.0</v>
@@ -2306,10 +2308,10 @@
         <v>851.0</v>
       </c>
       <c r="I27" s="2">
-        <v>828.0</v>
+        <v>838.0</v>
       </c>
       <c r="J27" s="2">
-        <v>801.0</v>
+        <v>814.0</v>
       </c>
       <c r="K27" s="2">
         <v>1.0</v>
@@ -2321,34 +2323,34 @@
         <v>0.0</v>
       </c>
       <c r="N27" s="2">
-        <v>801.0</v>
+        <v>814.0</v>
       </c>
       <c r="O27" s="2">
-        <v>453.0</v>
+        <v>462.0</v>
       </c>
       <c r="P27" s="2">
-        <v>341.0</v>
+        <v>345.0</v>
       </c>
       <c r="Q27" s="2">
         <v>7.0</v>
       </c>
       <c r="R27" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="S27" s="2">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="T27" s="2">
         <v>3.0</v>
       </c>
       <c r="U27" s="2">
-        <v>21.0</v>
+        <v>10.0</v>
       </c>
       <c r="V27" s="2">
         <v>0.0</v>
       </c>
       <c r="W27" s="2">
-        <v>50.0</v>
+        <v>37.0</v>
       </c>
       <c r="X27" s="1">
         <v>1.0</v>
@@ -2457,7 +2459,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" s="2">
-        <v>1176.0</v>
+        <v>1183.0</v>
       </c>
       <c r="K29" s="2">
         <v>1.0</v>
@@ -2469,7 +2471,7 @@
         <v>0.0</v>
       </c>
       <c r="N29" s="2">
-        <v>1176.0</v>
+        <v>1183.0</v>
       </c>
       <c r="O29" s="2">
         <v>445.0</v>
@@ -2478,7 +2480,7 @@
         <v>437.0</v>
       </c>
       <c r="Q29" s="2">
-        <v>294.0</v>
+        <v>301.0</v>
       </c>
       <c r="R29" s="2">
         <v>47.0</v>
@@ -3656,13 +3658,13 @@
         <v>1100.0</v>
       </c>
       <c r="O45" s="2">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="P45" s="2">
         <v>544.0</v>
       </c>
       <c r="Q45" s="2">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="R45" s="2">
         <v>51.0</v>
@@ -4233,7 +4235,7 @@
         <v>834.0</v>
       </c>
       <c r="J53" s="2">
-        <v>820.0</v>
+        <v>822.0</v>
       </c>
       <c r="K53" s="2">
         <v>1.0</v>
@@ -4245,13 +4247,13 @@
         <v>0.0</v>
       </c>
       <c r="N53" s="2">
-        <v>820.0</v>
+        <v>822.0</v>
       </c>
       <c r="O53" s="2">
         <v>449.0</v>
       </c>
       <c r="P53" s="2">
-        <v>365.0</v>
+        <v>367.0</v>
       </c>
       <c r="Q53" s="2">
         <v>6.0</v>
@@ -4260,7 +4262,7 @@
         <v>6.0</v>
       </c>
       <c r="S53" s="2">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="T53" s="2">
         <v>5.0</v>
@@ -4272,7 +4274,7 @@
         <v>0.0</v>
       </c>
       <c r="W53" s="2">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="X53" s="1">
         <v>1.0</v>
@@ -5195,7 +5197,7 @@
         <v>1155.0</v>
       </c>
       <c r="J66" s="2">
-        <v>1065.0</v>
+        <v>1066.0</v>
       </c>
       <c r="K66" s="2">
         <v>1.0</v>
@@ -5207,10 +5209,10 @@
         <v>0.0</v>
       </c>
       <c r="N66" s="2">
-        <v>1065.0</v>
+        <v>1066.0</v>
       </c>
       <c r="O66" s="2">
-        <v>579.0</v>
+        <v>580.0</v>
       </c>
       <c r="P66" s="2">
         <v>479.0</v>
@@ -5222,7 +5224,7 @@
         <v>27.0</v>
       </c>
       <c r="S66" s="2">
-        <v>59.0</v>
+        <v>58.0</v>
       </c>
       <c r="T66" s="2">
         <v>4.0</v>
@@ -5234,7 +5236,7 @@
         <v>0.0</v>
       </c>
       <c r="W66" s="2">
-        <v>90.0</v>
+        <v>89.0</v>
       </c>
       <c r="X66" s="1">
         <v>1.0</v>
@@ -7045,7 +7047,7 @@
         <v>940.0</v>
       </c>
       <c r="J91" s="2">
-        <v>729.0</v>
+        <v>744.0</v>
       </c>
       <c r="K91" s="2">
         <v>1.0</v>
@@ -7057,34 +7059,34 @@
         <v>0.0</v>
       </c>
       <c r="N91" s="2">
-        <v>729.0</v>
+        <v>744.0</v>
       </c>
       <c r="O91" s="2">
-        <v>263.0</v>
+        <v>272.0</v>
       </c>
       <c r="P91" s="2">
-        <v>348.0</v>
+        <v>351.0</v>
       </c>
       <c r="Q91" s="2">
-        <v>118.0</v>
+        <v>121.0</v>
       </c>
       <c r="R91" s="2">
         <v>44.0</v>
       </c>
       <c r="S91" s="2">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
       <c r="T91" s="2">
         <v>4.0</v>
       </c>
       <c r="U91" s="2">
-        <v>129.0</v>
+        <v>119.0</v>
       </c>
       <c r="V91" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W91" s="2">
-        <v>211.0</v>
+        <v>196.0</v>
       </c>
       <c r="X91" s="1">
         <v>1.0</v>
@@ -7563,7 +7565,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>1404.0</v>
+        <v>1405.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7575,10 +7577,10 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>1404.0</v>
+        <v>1405.0</v>
       </c>
       <c r="O98" s="2">
-        <v>752.0</v>
+        <v>753.0</v>
       </c>
       <c r="P98" s="2">
         <v>629.0</v>
@@ -7590,7 +7592,7 @@
         <v>16.0</v>
       </c>
       <c r="S98" s="2">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
       <c r="T98" s="2">
         <v>8.0</v>
@@ -7602,7 +7604,7 @@
         <v>1.0</v>
       </c>
       <c r="W98" s="2">
-        <v>57.0</v>
+        <v>56.0</v>
       </c>
       <c r="X98" s="1">
         <v>1.0</v>
@@ -9946,13 +9948,13 @@
         <v>729.0</v>
       </c>
       <c r="O130" s="2">
-        <v>478.0</v>
+        <v>479.0</v>
       </c>
       <c r="P130" s="2">
         <v>204.0</v>
       </c>
       <c r="Q130" s="2">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
       <c r="R130" s="2">
         <v>30.0</v>
@@ -10227,7 +10229,7 @@
         <v>1343.0</v>
       </c>
       <c r="J134" s="2">
-        <v>1219.0</v>
+        <v>1218.0</v>
       </c>
       <c r="K134" s="2">
         <v>1.0</v>
@@ -10239,19 +10241,19 @@
         <v>0.0</v>
       </c>
       <c r="N134" s="2">
-        <v>1219.0</v>
+        <v>1218.0</v>
       </c>
       <c r="O134" s="2">
         <v>749.0</v>
       </c>
       <c r="P134" s="2">
-        <v>399.0</v>
+        <v>398.0</v>
       </c>
       <c r="Q134" s="2">
         <v>71.0</v>
       </c>
       <c r="R134" s="2">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="S134" s="2">
         <v>62.0</v>
@@ -10266,7 +10268,7 @@
         <v>2.0</v>
       </c>
       <c r="W134" s="2">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="X134" s="1">
         <v>1.0</v>
@@ -11189,7 +11191,7 @@
         <v>1424.0</v>
       </c>
       <c r="J147" s="2">
-        <v>1207.0</v>
+        <v>1276.0</v>
       </c>
       <c r="K147" s="2">
         <v>1.0</v>
@@ -11201,13 +11203,13 @@
         <v>0.0</v>
       </c>
       <c r="N147" s="2">
-        <v>1207.0</v>
+        <v>1276.0</v>
       </c>
       <c r="O147" s="2">
-        <v>620.0</v>
+        <v>660.0</v>
       </c>
       <c r="P147" s="2">
-        <v>572.0</v>
+        <v>601.0</v>
       </c>
       <c r="Q147" s="2">
         <v>15.0</v>
@@ -14075,7 +14077,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" s="2">
-        <v>974.0</v>
+        <v>977.0</v>
       </c>
       <c r="K186" s="2">
         <v>1.0</v>
@@ -14087,34 +14089,34 @@
         <v>0.0</v>
       </c>
       <c r="N186" s="2">
-        <v>974.0</v>
+        <v>977.0</v>
       </c>
       <c r="O186" s="2">
         <v>304.0</v>
       </c>
       <c r="P186" s="2">
-        <v>401.0</v>
+        <v>403.0</v>
       </c>
       <c r="Q186" s="2">
-        <v>269.0</v>
+        <v>270.0</v>
       </c>
       <c r="R186" s="2">
         <v>18.0</v>
       </c>
       <c r="S186" s="2">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
       <c r="T186" s="2">
         <v>0.0</v>
       </c>
       <c r="U186" s="2">
-        <v>36.0</v>
+        <v>34.0</v>
       </c>
       <c r="V186" s="2">
         <v>0.0</v>
       </c>
       <c r="W186" s="2">
-        <v>93.0</v>
+        <v>90.0</v>
       </c>
       <c r="X186" s="1">
         <v>1.0</v>
@@ -14756,13 +14758,13 @@
         <v>538.0</v>
       </c>
       <c r="O195" s="2">
-        <v>306.0</v>
+        <v>323.0</v>
       </c>
       <c r="P195" s="2">
         <v>213.0</v>
       </c>
       <c r="Q195" s="2">
-        <v>19.0</v>
+        <v>2.0</v>
       </c>
       <c r="R195" s="2">
         <v>13.0</v>
@@ -15061,7 +15063,7 @@
         <v>4.0</v>
       </c>
       <c r="R199" s="2">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="S199" s="2">
         <v>41.0</v>
@@ -15073,7 +15075,7 @@
         <v>0.0</v>
       </c>
       <c r="V199" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W199" s="2">
         <v>107.0</v>
@@ -15259,7 +15261,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>1105.0</v>
+        <v>1110.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -15271,13 +15273,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>1105.0</v>
+        <v>1110.0</v>
       </c>
       <c r="O202" s="2">
-        <v>673.0</v>
+        <v>675.0</v>
       </c>
       <c r="P202" s="2">
-        <v>432.0</v>
+        <v>435.0</v>
       </c>
       <c r="Q202" s="2">
         <v>0.0</v>
@@ -15286,19 +15288,19 @@
         <v>8.0</v>
       </c>
       <c r="S202" s="2">
-        <v>29.0</v>
+        <v>26.0</v>
       </c>
       <c r="T202" s="2">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="U202" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="V202" s="2">
         <v>1.0</v>
       </c>
       <c r="W202" s="2">
-        <v>67.0</v>
+        <v>62.0</v>
       </c>
       <c r="X202" s="1">
         <v>1.0</v>
@@ -15407,7 +15409,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" s="2">
-        <v>1141.0</v>
+        <v>1154.0</v>
       </c>
       <c r="K204" s="2">
         <v>1.0</v>
@@ -15419,34 +15421,34 @@
         <v>0.0</v>
       </c>
       <c r="N204" s="2">
-        <v>1141.0</v>
+        <v>1154.0</v>
       </c>
       <c r="O204" s="2">
-        <v>618.0</v>
+        <v>624.0</v>
       </c>
       <c r="P204" s="2">
-        <v>498.0</v>
+        <v>503.0</v>
       </c>
       <c r="Q204" s="2">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="R204" s="2">
-        <v>38.0</v>
+        <v>36.0</v>
       </c>
       <c r="S204" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="T204" s="2">
         <v>0.0</v>
       </c>
       <c r="U204" s="2">
-        <v>41.0</v>
+        <v>28.0</v>
       </c>
       <c r="V204" s="2">
         <v>0.0</v>
       </c>
       <c r="W204" s="2">
-        <v>94.0</v>
+        <v>81.0</v>
       </c>
       <c r="X204" s="1">
         <v>1.0</v>
@@ -15481,7 +15483,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" s="2">
-        <v>817.0</v>
+        <v>819.0</v>
       </c>
       <c r="K205" s="2">
         <v>1.0</v>
@@ -15493,10 +15495,10 @@
         <v>0.0</v>
       </c>
       <c r="N205" s="2">
-        <v>817.0</v>
+        <v>819.0</v>
       </c>
       <c r="O205" s="2">
-        <v>446.0</v>
+        <v>448.0</v>
       </c>
       <c r="P205" s="2">
         <v>320.0</v>
@@ -15508,7 +15510,7 @@
         <v>47.0</v>
       </c>
       <c r="S205" s="2">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
       <c r="T205" s="2">
         <v>2.0</v>
@@ -15520,7 +15522,7 @@
         <v>0.0</v>
       </c>
       <c r="W205" s="2">
-        <v>80.0</v>
+        <v>78.0</v>
       </c>
       <c r="X205" s="1">
         <v>1.0</v>
@@ -15925,7 +15927,7 @@
         <v>1074.0</v>
       </c>
       <c r="J211" s="2">
-        <v>918.0</v>
+        <v>924.0</v>
       </c>
       <c r="K211" s="2">
         <v>1.0</v>
@@ -15937,34 +15939,34 @@
         <v>0.0</v>
       </c>
       <c r="N211" s="2">
-        <v>917.0</v>
+        <v>924.0</v>
       </c>
       <c r="O211" s="2">
-        <v>469.0</v>
+        <v>470.0</v>
       </c>
       <c r="P211" s="2">
-        <v>432.0</v>
+        <v>437.0</v>
       </c>
       <c r="Q211" s="2">
         <v>17.0</v>
       </c>
       <c r="R211" s="2">
-        <v>88.0</v>
+        <v>86.0</v>
       </c>
       <c r="S211" s="2">
         <v>46.0</v>
       </c>
       <c r="T211" s="2">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="U211" s="2">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="V211" s="2">
         <v>1.0</v>
       </c>
       <c r="W211" s="2">
-        <v>156.0</v>
+        <v>150.0</v>
       </c>
       <c r="X211" s="1">
         <v>1.0</v>
@@ -16147,7 +16149,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" s="2">
-        <v>894.0</v>
+        <v>896.0</v>
       </c>
       <c r="K214" s="2">
         <v>1.0</v>
@@ -16159,13 +16161,13 @@
         <v>0.0</v>
       </c>
       <c r="N214" s="2">
-        <v>894.0</v>
+        <v>896.0</v>
       </c>
       <c r="O214" s="2">
-        <v>474.0</v>
+        <v>475.0</v>
       </c>
       <c r="P214" s="2">
-        <v>420.0</v>
+        <v>421.0</v>
       </c>
       <c r="Q214" s="2">
         <v>0.0</v>
@@ -16180,13 +16182,13 @@
         <v>7.0</v>
       </c>
       <c r="U214" s="2">
-        <v>74.0</v>
+        <v>72.0</v>
       </c>
       <c r="V214" s="2">
         <v>5.0</v>
       </c>
       <c r="W214" s="2">
-        <v>144.0</v>
+        <v>142.0</v>
       </c>
       <c r="X214" s="1">
         <v>1.0</v>
@@ -16606,13 +16608,13 @@
         <v>767.0</v>
       </c>
       <c r="O220" s="2">
-        <v>222.0</v>
+        <v>250.0</v>
       </c>
       <c r="P220" s="2">
         <v>343.0</v>
       </c>
       <c r="Q220" s="2">
-        <v>202.0</v>
+        <v>174.0</v>
       </c>
       <c r="R220" s="2">
         <v>16.0</v>
@@ -16680,13 +16682,13 @@
         <v>823.0</v>
       </c>
       <c r="O221" s="2">
-        <v>270.0</v>
+        <v>329.0</v>
       </c>
       <c r="P221" s="2">
-        <v>321.0</v>
+        <v>335.0</v>
       </c>
       <c r="Q221" s="2">
-        <v>232.0</v>
+        <v>159.0</v>
       </c>
       <c r="R221" s="2">
         <v>9.0</v>
